--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -27305,6 +27305,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1172">
+      <c r="A1172" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1172" t="n">
+        <v>48840</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>6.61999988555908</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>6.28000020980835</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>6.30999994277954</v>
+      </c>
+      <c r="G1172" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -27328,6 +27328,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1173">
+      <c r="A1173" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1173" t="n">
+        <v>55008</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>6.32999992370605</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1173" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -27351,6 +27351,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1174">
+      <c r="A1174" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1174" t="n">
+        <v>28019</v>
+      </c>
+      <c r="C1174" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>6.03000020980835</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>6.03000020980835</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>6.05999994277954</v>
+      </c>
+      <c r="G1174" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -27374,6 +27374,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1175">
+      <c r="A1175" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1175" t="n">
+        <v>28542</v>
+      </c>
+      <c r="C1175" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>6.07000017166138</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>6.07999992370605</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>6.07999992370605</v>
+      </c>
+      <c r="G1175" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -27215,22 +27215,22 @@
     </row>
     <row r="1168">
       <c r="A1168" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1168" t="n">
-        <v>14083</v>
+        <v>28000</v>
       </c>
       <c r="C1168" t="n">
-        <v>6.92000007629395</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="D1168" t="n">
-        <v>6.82000017166138</v>
+        <v>6.84999990463257</v>
       </c>
       <c r="E1168" t="n">
-        <v>6.8899998664856</v>
+        <v>7.01999998092651</v>
       </c>
       <c r="F1168" t="n">
-        <v>6.90999984741211</v>
+        <v>6.88000011444092</v>
       </c>
       <c r="G1168" t="s">
         <v>7</v>
@@ -27238,22 +27238,22 @@
     </row>
     <row r="1169">
       <c r="A1169" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1169" t="n">
-        <v>18166</v>
+        <v>14083</v>
       </c>
       <c r="C1169" t="n">
-        <v>6.98000001907349</v>
+        <v>6.92000007629395</v>
       </c>
       <c r="D1169" t="n">
-        <v>6.80999994277954</v>
+        <v>6.82000017166138</v>
       </c>
       <c r="E1169" t="n">
         <v>6.8899998664856</v>
       </c>
       <c r="F1169" t="n">
-        <v>6.8600001335144</v>
+        <v>6.90999984741211</v>
       </c>
       <c r="G1169" t="s">
         <v>7</v>
@@ -27261,22 +27261,22 @@
     </row>
     <row r="1170">
       <c r="A1170" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1170" t="n">
-        <v>22812</v>
+        <v>18166</v>
       </c>
       <c r="C1170" t="n">
-        <v>7.03999996185303</v>
+        <v>6.98000001907349</v>
       </c>
       <c r="D1170" t="n">
-        <v>6.82999992370605</v>
+        <v>6.80999994277954</v>
       </c>
       <c r="E1170" t="n">
+        <v>6.8899998664856</v>
+      </c>
+      <c r="F1170" t="n">
         <v>6.8600001335144</v>
-      </c>
-      <c r="F1170" t="n">
-        <v>7</v>
       </c>
       <c r="G1170" t="s">
         <v>7</v>
@@ -27284,22 +27284,22 @@
     </row>
     <row r="1171">
       <c r="A1171" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1171" t="n">
-        <v>111772</v>
+        <v>22812</v>
       </c>
       <c r="C1171" t="n">
-        <v>6.76999998092651</v>
+        <v>7.03999996185303</v>
       </c>
       <c r="D1171" t="n">
-        <v>6.46000003814697</v>
+        <v>6.82999992370605</v>
       </c>
       <c r="E1171" t="n">
-        <v>6.73999977111816</v>
+        <v>6.8600001335144</v>
       </c>
       <c r="F1171" t="n">
-        <v>6.55999994277954</v>
+        <v>7</v>
       </c>
       <c r="G1171" t="s">
         <v>7</v>
@@ -27307,22 +27307,22 @@
     </row>
     <row r="1172">
       <c r="A1172" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1172" t="n">
-        <v>48840</v>
+        <v>111772</v>
       </c>
       <c r="C1172" t="n">
-        <v>6.61999988555908</v>
+        <v>6.76999998092651</v>
       </c>
       <c r="D1172" t="n">
-        <v>6.28000020980835</v>
+        <v>6.46000003814697</v>
       </c>
       <c r="E1172" t="n">
-        <v>6.57999992370605</v>
+        <v>6.73999977111816</v>
       </c>
       <c r="F1172" t="n">
-        <v>6.30999994277954</v>
+        <v>6.55999994277954</v>
       </c>
       <c r="G1172" t="s">
         <v>7</v>
@@ -27330,22 +27330,22 @@
     </row>
     <row r="1173">
       <c r="A1173" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1173" t="n">
-        <v>55008</v>
+        <v>48840</v>
       </c>
       <c r="C1173" t="n">
-        <v>6.32999992370605</v>
+        <v>6.61999988555908</v>
       </c>
       <c r="D1173" t="n">
-        <v>6</v>
+        <v>6.28000020980835</v>
       </c>
       <c r="E1173" t="n">
-        <v>6.30000019073486</v>
+        <v>6.57999992370605</v>
       </c>
       <c r="F1173" t="n">
-        <v>6</v>
+        <v>6.30999994277954</v>
       </c>
       <c r="G1173" t="s">
         <v>7</v>
@@ -27353,22 +27353,22 @@
     </row>
     <row r="1174">
       <c r="A1174" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1174" t="n">
-        <v>28019</v>
+        <v>55008</v>
       </c>
       <c r="C1174" t="n">
-        <v>6.15999984741211</v>
+        <v>6.32999992370605</v>
       </c>
       <c r="D1174" t="n">
-        <v>6.03000020980835</v>
+        <v>6</v>
       </c>
       <c r="E1174" t="n">
-        <v>6.03000020980835</v>
+        <v>6.30000019073486</v>
       </c>
       <c r="F1174" t="n">
-        <v>6.05999994277954</v>
+        <v>6</v>
       </c>
       <c r="G1174" t="s">
         <v>7</v>
@@ -27376,24 +27376,47 @@
     </row>
     <row r="1175">
       <c r="A1175" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1175" t="n">
-        <v>28542</v>
+        <v>28019</v>
       </c>
       <c r="C1175" t="n">
         <v>6.15999984741211</v>
       </c>
       <c r="D1175" t="n">
-        <v>6.07000017166138</v>
+        <v>6.03000020980835</v>
       </c>
       <c r="E1175" t="n">
-        <v>6.07999992370605</v>
+        <v>6.03000020980835</v>
       </c>
       <c r="F1175" t="n">
-        <v>6.07999992370605</v>
+        <v>6.05999994277954</v>
       </c>
       <c r="G1175" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1176" t="n">
+        <v>24692</v>
+      </c>
+      <c r="C1176" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>6.1399998664856</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="G1176" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -30985,7 +30985,7 @@
         <v>18838</v>
       </c>
       <c r="C1178" t="n">
-        <v>6.03999996185303</v>
+        <v>6.05000019073486</v>
       </c>
       <c r="D1178" t="n">
         <v>5.94999980926514</v>
@@ -31000,6 +31000,32 @@
         <v>6.05000019073486</v>
       </c>
       <c r="H1178" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1179" t="n">
+        <v>13605</v>
+      </c>
+      <c r="C1179" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>5.96999979019165</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>6.03000020980835</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="H1179" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -31029,6 +31029,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1180">
+      <c r="A1180" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1180" t="n">
+        <v>24877</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>5.98000001907349</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>6.03000020980835</v>
+      </c>
+      <c r="G1180" t="n">
+        <v>6.03000020980835</v>
+      </c>
+      <c r="H1180" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -31055,6 +31055,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1181">
+      <c r="A1181" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1181" t="n">
+        <v>14271</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>6.03999996185303</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>6.03999996185303</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>6.01000022888184</v>
+      </c>
+      <c r="G1181" t="n">
+        <v>6.01000022888184</v>
+      </c>
+      <c r="H1181" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -31081,6 +31081,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1182">
+      <c r="A1182" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1182" t="n">
+        <v>6446</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>5.94000005722046</v>
+      </c>
+      <c r="G1182" t="n">
+        <v>5.94000005722046</v>
+      </c>
+      <c r="H1182" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -31159,6 +31159,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1185">
+      <c r="A1185" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1185" t="n">
+        <v>13467</v>
+      </c>
+      <c r="C1185" t="n">
+        <v>6.01999998092651</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>5.90999984741211</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>5.98999977111816</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="H1185" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -27689,8 +27689,31 @@
       <c r="E1188" t="n">
         <v>5.82000017166138</v>
       </c>
-      <c r="F1188"/>
+      <c r="F1188" t="n">
+        <v>5.46000003814697</v>
+      </c>
       <c r="G1188" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1189" t="n">
+        <v>24370</v>
+      </c>
+      <c r="C1189" t="n">
+        <v>5.65999984741211</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="F1189"/>
+      <c r="G1189" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -27712,8 +27712,31 @@
       <c r="E1189" t="n">
         <v>5.46000003814697</v>
       </c>
-      <c r="F1189"/>
+      <c r="F1189" t="n">
+        <v>5.57000017166138</v>
+      </c>
       <c r="G1189" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1190" t="n">
+        <v>37500</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>5.63000011444092</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>5.34999990463257</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>5.57999992370605</v>
+      </c>
+      <c r="F1190"/>
+      <c r="G1190" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -27735,8 +27735,31 @@
       <c r="E1190" t="n">
         <v>5.57999992370605</v>
       </c>
-      <c r="F1190"/>
+      <c r="F1190" t="n">
+        <v>5.34999990463257</v>
+      </c>
       <c r="G1190" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1191" t="n">
+        <v>45298</v>
+      </c>
+      <c r="C1191" t="n">
+        <v>5.48000001907349</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>5.36999988555908</v>
+      </c>
+      <c r="F1191"/>
+      <c r="G1191" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -27758,8 +27758,31 @@
       <c r="E1191" t="n">
         <v>5.36999988555908</v>
       </c>
-      <c r="F1191"/>
+      <c r="F1191" t="n">
+        <v>5.34999990463257</v>
+      </c>
       <c r="G1191" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1192" t="n">
+        <v>37089</v>
+      </c>
+      <c r="C1192" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>5.40000009536743</v>
+      </c>
+      <c r="F1192"/>
+      <c r="G1192" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -27788,6 +27788,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1193" t="n">
+        <v>17890</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>5.42999982833862</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>5.40999984741211</v>
+      </c>
+      <c r="G1193" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -31445,6 +31445,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1196">
+      <c r="A1196" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1196" t="n">
+        <v>12314</v>
+      </c>
+      <c r="C1196" t="n">
+        <v>5.26999998092651</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="G1196" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="H1196" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -31471,6 +31471,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1197" t="n">
+        <v>19826</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>5.19000005722046</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>5.19000005722046</v>
+      </c>
+      <c r="G1197" t="n">
+        <v>5.19000005722046</v>
+      </c>
+      <c r="H1197" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -35120,6 +35120,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1199">
+      <c r="A1199" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1199" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="G1199" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="H1199" t="n">
+        <v>38471</v>
+      </c>
+      <c r="I1199" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -35149,6 +35149,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1200">
+      <c r="A1200" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1200" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1200" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G1200" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="H1200" t="n">
+        <v>16517</v>
+      </c>
+      <c r="I1200" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -35178,6 +35178,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1201">
+      <c r="A1201" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1201" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="G1201" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="H1201" t="n">
+        <v>23631</v>
+      </c>
+      <c r="I1201" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -35207,6 +35207,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1202">
+      <c r="A1202" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1202" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>4.94999980926514</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>4.96500015258789</v>
+      </c>
+      <c r="G1202" t="n">
+        <v>4.96500015258789</v>
+      </c>
+      <c r="H1202" t="n">
+        <v>15428</v>
+      </c>
+      <c r="I1202" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -35236,6 +35236,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1203">
+      <c r="A1203" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1203" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="G1203" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="H1203" t="n">
+        <v>25928</v>
+      </c>
+      <c r="I1203" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -35265,6 +35265,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1204">
+      <c r="A1204" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1204" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>4.98999977111816</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="G1204" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="H1204" t="n">
+        <v>28085</v>
+      </c>
+      <c r="I1204" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -35294,6 +35294,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1205">
+      <c r="A1205" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1205" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="G1205" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="H1205" t="n">
+        <v>18185</v>
+      </c>
+      <c r="I1205" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -35308,7 +35308,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="E1205" t="n">
-        <v>5.01000022888184</v>
+        <v>5</v>
       </c>
       <c r="F1205" t="n">
         <v>5.07999992370605</v>
@@ -35320,6 +35320,35 @@
         <v>18185</v>
       </c>
       <c r="I1205" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1206" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>5.32999992370605</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>5.28999996185303</v>
+      </c>
+      <c r="G1206" t="n">
+        <v>5.28999996185303</v>
+      </c>
+      <c r="H1206" t="n">
+        <v>32706</v>
+      </c>
+      <c r="I1206" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AGP.MI.xlsx
+++ b/data/AGP.MI.xlsx
@@ -35352,6 +35352,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1207">
+      <c r="A1207" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1207" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>5.23000001907349</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>5.30999994277954</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>5.21999979019165</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>5.23000001907349</v>
+      </c>
+      <c r="G1207" t="n">
+        <v>5.23000001907349</v>
+      </c>
+      <c r="H1207" t="n">
+        <v>7611</v>
+      </c>
+      <c r="I1207" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
